--- a/Planilha_Aluguel_Motos.xlsx
+++ b/Planilha_Aluguel_Motos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c901d2592481f9a/Área de Trabalho/Lucas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{46D65EAB-EC04-472E-862F-2175A03F3395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA064CE-643B-4500-A438-89155820984B}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{46D65EAB-EC04-472E-862F-2175A03F3395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE734BE8-F589-4709-8CD5-7BA255E7E523}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cadastro de Motos" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
   <si>
     <t>Modelo</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Pendente</t>
+  </si>
+  <si>
+    <t>teste</t>
   </si>
 </sst>
 </file>
@@ -664,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -850,6 +853,14 @@
       </c>
       <c r="I6" s="15">
         <v>11690</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="15">
+        <v>150000</v>
       </c>
     </row>
   </sheetData>
